--- a/Data for copy paste.xlsx
+++ b/Data for copy paste.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28803"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://towermint-my.sharepoint.com/personal/frank_vlotman_towermint_co_uk/Documents/Apps for Procurement/Linear Regression/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frank\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="13_ncr:1_{ADEBC1EC-1CAF-4945-A30F-48DD7C242B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9ABB88A6-00E5-41A2-8588-D30724CD200F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FEE5F3-F1DD-40B1-98A3-FBCD82210D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4710" yWindow="3750" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4356" yWindow="2652" windowWidth="16164" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -52,6 +52,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="mmm\-yyyy"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -95,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -104,6 +107,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -387,12 +393,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.85546875" style="1"/>
+    <col min="1" max="1" width="9.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="1"/>
+    <col min="5" max="5" width="9.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -418,9 +426,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
+        <v>45292</v>
       </c>
       <c r="B2" s="1">
         <v>150</v>
@@ -428,8 +436,8 @@
       <c r="C2" s="1">
         <v>120</v>
       </c>
-      <c r="E2" s="1">
-        <v>1</v>
+      <c r="E2" s="4">
+        <v>45292</v>
       </c>
       <c r="F2" s="1">
         <v>150</v>
@@ -444,9 +452,9 @@
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>45323</v>
       </c>
       <c r="B3" s="1">
         <v>160</v>
@@ -454,8 +462,8 @@
       <c r="C3" s="1">
         <v>170</v>
       </c>
-      <c r="E3" s="1">
-        <v>2</v>
+      <c r="E3" s="4">
+        <v>45323</v>
       </c>
       <c r="F3" s="1">
         <v>130</v>
@@ -470,9 +478,9 @@
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>45352</v>
       </c>
       <c r="B4" s="1">
         <v>165</v>
@@ -480,8 +488,8 @@
       <c r="C4" s="1">
         <v>155</v>
       </c>
-      <c r="E4" s="1">
-        <v>3</v>
+      <c r="E4" s="4">
+        <v>45352</v>
       </c>
       <c r="F4" s="1">
         <v>140</v>
@@ -496,9 +504,9 @@
         <v>231</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>45383</v>
       </c>
       <c r="B5" s="1">
         <v>170</v>
@@ -506,8 +514,8 @@
       <c r="C5" s="1">
         <v>160</v>
       </c>
-      <c r="E5" s="1">
-        <v>4</v>
+      <c r="E5" s="4">
+        <v>45383</v>
       </c>
       <c r="F5" s="1">
         <v>120</v>
@@ -522,9 +530,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>45413</v>
       </c>
       <c r="B6" s="1">
         <v>180</v>
@@ -532,8 +540,8 @@
       <c r="C6" s="1">
         <v>170</v>
       </c>
-      <c r="E6" s="1">
-        <v>5</v>
+      <c r="E6" s="4">
+        <v>45413</v>
       </c>
       <c r="F6" s="1">
         <v>160</v>
@@ -548,9 +556,9 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>45444</v>
       </c>
       <c r="B7" s="1">
         <v>185</v>
@@ -558,8 +566,8 @@
       <c r="C7" s="1">
         <v>185</v>
       </c>
-      <c r="E7" s="1">
-        <v>6</v>
+      <c r="E7" s="4">
+        <v>45444</v>
       </c>
       <c r="F7" s="1">
         <v>145</v>
@@ -574,9 +582,9 @@
         <v>286</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>45474</v>
       </c>
       <c r="B8" s="1">
         <v>190</v>
@@ -584,8 +592,8 @@
       <c r="C8" s="1">
         <v>190</v>
       </c>
-      <c r="E8" s="1">
-        <v>7</v>
+      <c r="E8" s="4">
+        <v>45474</v>
       </c>
       <c r="F8" s="1">
         <v>120</v>
@@ -600,9 +608,9 @@
         <v>327</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>45505</v>
       </c>
       <c r="B9" s="1">
         <v>200</v>
@@ -610,8 +618,8 @@
       <c r="C9" s="1">
         <v>175</v>
       </c>
-      <c r="E9" s="1">
-        <v>8</v>
+      <c r="E9" s="4">
+        <v>45505</v>
       </c>
       <c r="F9" s="1">
         <v>170</v>
@@ -626,9 +634,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>45536</v>
       </c>
       <c r="B10" s="1">
         <v>210</v>
@@ -636,8 +644,8 @@
       <c r="C10" s="1">
         <v>180</v>
       </c>
-      <c r="E10" s="1">
-        <v>9</v>
+      <c r="E10" s="4">
+        <v>45536</v>
       </c>
       <c r="F10" s="1">
         <v>155</v>
@@ -652,9 +660,9 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>10</v>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>45566</v>
       </c>
       <c r="B11" s="1">
         <v>220</v>
@@ -662,8 +670,8 @@
       <c r="C11" s="1">
         <v>185</v>
       </c>
-      <c r="E11" s="1">
-        <v>10</v>
+      <c r="E11" s="4">
+        <v>45566</v>
       </c>
       <c r="F11" s="1">
         <v>160</v>
@@ -678,9 +686,9 @@
         <v>204</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>11</v>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
+        <v>45597</v>
       </c>
       <c r="B12" s="1">
         <v>230</v>
@@ -688,8 +696,8 @@
       <c r="C12" s="1">
         <v>200</v>
       </c>
-      <c r="E12" s="1">
-        <v>11</v>
+      <c r="E12" s="4">
+        <v>45597</v>
       </c>
       <c r="F12" s="1">
         <v>170</v>
@@ -704,9 +712,9 @@
         <v>245</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>12</v>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>45627</v>
       </c>
       <c r="B13" s="1">
         <v>240</v>
@@ -714,8 +722,8 @@
       <c r="C13" s="1">
         <v>170</v>
       </c>
-      <c r="E13" s="1">
-        <v>12</v>
+      <c r="E13" s="4">
+        <v>45627</v>
       </c>
       <c r="F13" s="1">
         <v>185</v>
@@ -730,9 +738,9 @@
         <v>176</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E14" s="1">
-        <v>13</v>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E14" s="4">
+        <v>45658</v>
       </c>
       <c r="F14" s="1">
         <v>190</v>
@@ -741,9 +749,9 @@
         <v>500</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E15" s="1">
-        <v>14</v>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E15" s="4">
+        <v>45689</v>
       </c>
       <c r="F15" s="1">
         <v>175</v>
@@ -752,9 +760,9 @@
         <v>480</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E16" s="1">
-        <v>15</v>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E16" s="4">
+        <v>45717</v>
       </c>
       <c r="F16" s="1">
         <v>180</v>
@@ -763,9 +771,9 @@
         <v>500</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="E17" s="1">
-        <v>16</v>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="E17" s="4">
+        <v>45748</v>
       </c>
       <c r="F17" s="1">
         <v>185</v>
@@ -774,9 +782,9 @@
         <v>480</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="E18" s="1">
-        <v>17</v>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="E18" s="4">
+        <v>45778</v>
       </c>
       <c r="F18" s="1">
         <v>200</v>
@@ -785,9 +793,9 @@
         <v>500</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="E19" s="1">
-        <v>18</v>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="E19" s="4">
+        <v>45809</v>
       </c>
       <c r="F19" s="1">
         <v>170</v>
@@ -796,7 +804,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="2"/>
     </row>
   </sheetData>
